--- a/Server_Build_DOC.xlsx
+++ b/Server_Build_DOC.xlsx
@@ -9,10 +9,11 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15345" windowHeight="4635"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15345" windowHeight="4635" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Docker" sheetId="1" r:id="rId1"/>
+    <sheet name="CI_CD" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="61">
   <si>
     <t>============================================================</t>
   </si>
@@ -171,6 +172,42 @@
   </si>
   <si>
     <t>    docker exec -it &lt;container_name&gt; bash # Truy cập vào terminal của container</t>
+  </si>
+  <si>
+    <t>===== DEPLOY TO VPS=========</t>
+  </si>
+  <si>
+    <t>CI-CD với GitHub Actions:</t>
+  </si>
+  <si>
+    <t>Deploy thủ công:</t>
+  </si>
+  <si>
+    <t>    1. Cài đặt Docker và Docker Compose trên VPS.</t>
+  </si>
+  <si>
+    <t>    - Hiện tại đang dùng google cloud</t>
+  </si>
+  <si>
+    <t>    2. Clone repository của bạn vào VPS.</t>
+  </si>
+  <si>
+    <t>    3. Chạy lệnh docker compose up -d --build để khởi động ứng dụng.</t>
+  </si>
+  <si>
+    <t>    1. Tạo file workflow trong thư mục .github/workflows/ (ví dụ: deploy.yml).</t>
+  </si>
+  <si>
+    <t>    2. Sử dụng SSH để kết nối và chạy lệnh deploy trên VPS từ workflow.</t>
+  </si>
+  <si>
+    <t>    - Tạo SSH key pair và thêm public key vào VPS.</t>
+  </si>
+  <si>
+    <t>    - Thêm private key vào GitHub Secrets (Settings &gt; Secrets &gt; Actions).</t>
+  </si>
+  <si>
+    <t>    3. Cấu hình workflow để tự động deploy khi có push lên branch main.</t>
   </si>
 </sst>
 </file>
@@ -253,6 +290,163 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>352425</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>9524</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>49413</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="352425" y="2962275"/>
+          <a:ext cx="2705099" cy="2421138"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>352425</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>152401</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>309628</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>38101</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3400425" y="3009901"/>
+          <a:ext cx="2395603" cy="3886200"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>219075</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>47626</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>212030</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>123826</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6315075" y="2905126"/>
+          <a:ext cx="4260155" cy="3886200"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>390173</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>142690</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9763125" y="1524000"/>
+          <a:ext cx="2819048" cy="1476190"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1197,4 +1391,84 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:B15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="16384" width="9.140625" style="5"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B2" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B3" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B4" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B5" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B6" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="7" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B7" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B8" s="6"/>
+    </row>
+    <row r="9" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B9" s="6"/>
+    </row>
+    <row r="10" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B10" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B11" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="12" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B12" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="13" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B13" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="14" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B14" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="15" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B15" s="4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>